--- a/R-dataprocessor/submodules/manual_start/Fallvignette_Process_Evaluation/R-Fallvignette_Process_Evaluation/inst/extdata/WP8MRP_Liste_Daten_Mapping20260722.xlsx
+++ b/R-dataprocessor/submodules/manual_start/Fallvignette_Process_Evaluation/R-Fallvignette_Process_Evaluation/inst/extdata/WP8MRP_Liste_Daten_Mapping20260722.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6A06D7-04C5-4693-89AC-F1482AA91ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="WP8MRPListe_ImportTemplate_2026" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="WP8MRPListe_ImportTemplate_2026" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -20,363 +28,371 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="106">
-  <si>
-    <t xml:space="preserve">Fallvignette</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
+  <si>
+    <t>Fallvignette</t>
   </si>
   <si>
     <t xml:space="preserve">Quelle </t>
   </si>
   <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kommentar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">record_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">generiert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standortübergreifend eindeutig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_mrp_fachbereich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mapping aus WP8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_fv_alter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fall_age_at_admission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aus fall_fe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_fv_geschlecht</t>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Kommentar</t>
+  </si>
+  <si>
+    <t>record_id</t>
+  </si>
+  <si>
+    <t>generiert</t>
+  </si>
+  <si>
+    <t>Standortübergreifend eindeutig</t>
+  </si>
+  <si>
+    <t>wp8_mrp_fachbereich</t>
+  </si>
+  <si>
+    <t>wp8_fv_alter</t>
+  </si>
+  <si>
+    <t>fall_age_at_admission</t>
+  </si>
+  <si>
+    <t>Aus fall_fe</t>
+  </si>
+  <si>
+    <t>wp8_fv_geschlecht</t>
   </si>
   <si>
     <t xml:space="preserve">pat_geschlecht </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_fv_gewicht</t>
+    <t>wp8_fv_gewicht</t>
   </si>
   <si>
     <t xml:space="preserve">meda_gewicht_aktuell </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_fv_schwanger_mo</t>
+    <t>wp8_fv_schwanger_mo</t>
   </si>
   <si>
     <t xml:space="preserve">meda_schwanger_mo </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_fv_diagnosen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inhalt und Zeiträume mit WP8 
+    <t>wp8_fv_diagnosen</t>
+  </si>
+  <si>
+    <t>Inhalt und Zeiträume mit WP8 
 Besprechen</t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_fv_medikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_fv_laborparameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_fv_op</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja/Nein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_kurzbeschr</t>
+    <t>wp8_fv_medikation</t>
+  </si>
+  <si>
+    <t>wp8_fv_laborparameter</t>
+  </si>
+  <si>
+    <t>wp8_fv_op</t>
+  </si>
+  <si>
+    <t>Ja/Nein</t>
+  </si>
+  <si>
+    <t>wp8_ret_kurzbeschr</t>
   </si>
   <si>
     <t xml:space="preserve">ret_kurzbeschr </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_ret_ip_klasse_01</t>
+    <t>wp8_ret_ip_klasse_01</t>
   </si>
   <si>
     <t xml:space="preserve">ret_ip_klasse_01 </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_ret_atc1_2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_atc1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_atc2_2026</t>
+    <t>wp8_ret_atc1_2026</t>
+  </si>
+  <si>
+    <t>ret_atc1</t>
+  </si>
+  <si>
+    <t>wp8_ret_atc2_2026</t>
   </si>
   <si>
     <t xml:space="preserve">ret_atc2 </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_ret_ip_klasse_disease</t>
+    <t>wp8_ret_ip_klasse_disease</t>
   </si>
   <si>
     <t xml:space="preserve">ret_ip_klasse_disease </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_ret_gewissheit</t>
+    <t>wp8_ret_gewissheit</t>
   </si>
   <si>
     <t xml:space="preserve">ret_gewissheit1 </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_ret_gewiss_grund_abl_01</t>
+    <t>wp8_ret_gewiss_grund_abl_01</t>
   </si>
   <si>
     <t xml:space="preserve">ret_gewiss_grund1_abl_01 </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_ret_gewiss_grund_abl_klin</t>
+    <t>wp8_ret_gewiss_grund_abl_klin</t>
   </si>
   <si>
     <t xml:space="preserve">ret_gewiss_grund_abl_klin1 </t>
   </si>
   <si>
-    <t xml:space="preserve">wp8_ret_gewiss_grund_abl_klin_neg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_gewiss_grund_abl_klin1_neg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_am___10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am1___10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_orga___1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga1___1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_orga___2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga1___2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_orga___3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga1___3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_orga___4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga1___4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_orga___5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga1___5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_orga___6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga1___6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_orga___7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga1___7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_massn_orga___8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga1___8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp8_ret_notiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_notiz1</t>
+    <t>wp8_ret_gewiss_grund_abl_klin_neg</t>
+  </si>
+  <si>
+    <t>ret_gewiss_grund_abl_klin1_neg</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___1</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___1</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___2</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___2</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___3</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___3</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___4</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___4</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___5</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___5</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___6</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___6</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___7</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___7</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___8</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___8</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___9</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___9</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_am___10</t>
+  </si>
+  <si>
+    <t>ret_massn_am1___10</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_orga___1</t>
+  </si>
+  <si>
+    <t>ret_massn_orga1___1</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_orga___2</t>
+  </si>
+  <si>
+    <t>ret_massn_orga1___2</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_orga___3</t>
+  </si>
+  <si>
+    <t>ret_massn_orga1___3</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_orga___4</t>
+  </si>
+  <si>
+    <t>ret_massn_orga1___4</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_orga___5</t>
+  </si>
+  <si>
+    <t>ret_massn_orga1___5</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_orga___6</t>
+  </si>
+  <si>
+    <t>ret_massn_orga1___6</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_orga___7</t>
+  </si>
+  <si>
+    <t>ret_massn_orga1___7</t>
+  </si>
+  <si>
+    <t>wp8_ret_massn_orga___8</t>
+  </si>
+  <si>
+    <t>ret_massn_orga1___8</t>
+  </si>
+  <si>
+    <t>wp8_ret_notiz</t>
+  </si>
+  <si>
+    <t>ret_notiz1</t>
   </si>
   <si>
     <t xml:space="preserve">ret_gewiss_grund2_abl_01 </t>
   </si>
   <si>
-    <t xml:space="preserve">Ein retMRP kann zwei Bewertungen haben,
+    <t>Ein retMRP kann zwei Bewertungen haben,
 Die je eine eigene Zeile bekommen.</t>
   </si>
   <si>
-    <t xml:space="preserve">ret_gewiss_grund_abl_klin2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_gewiss_grund_abl_klin2_neg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_am2___10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga2___1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga2___2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga2___3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga2___4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga2___5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga2___6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga2___7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_massn_orga2___8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_notiz2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mrp_auswahl_complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select wenn Broad Consent und (ret_gewiss_grund1_abl_01 und/oder ret_gewiss_grund2_abl_01 =3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test-MRPs nicht berücksichtigen</t>
+    <t>ret_gewiss_grund_abl_klin2</t>
+  </si>
+  <si>
+    <t>ret_gewiss_grund_abl_klin2_neg</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___1</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___2</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___3</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___4</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___5</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___6</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___7</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___8</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___9</t>
+  </si>
+  <si>
+    <t>ret_massn_am2___10</t>
+  </si>
+  <si>
+    <t>ret_massn_orga2___1</t>
+  </si>
+  <si>
+    <t>ret_massn_orga2___2</t>
+  </si>
+  <si>
+    <t>ret_massn_orga2___3</t>
+  </si>
+  <si>
+    <t>ret_massn_orga2___4</t>
+  </si>
+  <si>
+    <t>ret_massn_orga2___5</t>
+  </si>
+  <si>
+    <t>ret_massn_orga2___6</t>
+  </si>
+  <si>
+    <t>ret_massn_orga2___7</t>
+  </si>
+  <si>
+    <t>ret_massn_orga2___8</t>
+  </si>
+  <si>
+    <t>ret_notiz2</t>
+  </si>
+  <si>
+    <t>mrp_auswahl_complete</t>
+  </si>
+  <si>
+    <t>Select wenn Broad Consent und (ret_gewiss_grund1_abl_01 und/oder ret_gewiss_grund2_abl_01 =3)</t>
+  </si>
+  <si>
+    <t>Test-MRPs nicht berücksichtigen</t>
+  </si>
+  <si>
+    <t>wp8_standort_id</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mapping aus WP8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / Bzw. Mapping aus der Tabelle von Tatjana</t>
+    </r>
+  </si>
+  <si>
+    <t>Id für den Datensatz, die auf Herkunftsstandort rückschließen lässt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -388,7 +404,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -396,152 +412,225 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -549,24 +638,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -579,7 +677,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -589,13 +693,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -603,6 +709,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -610,34 +717,38 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D95"/>
-  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D96"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="65.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="11.57"/>
+    <col min="1" max="1" width="54.88671875" customWidth="1"/>
+    <col min="2" max="2" width="67" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="5" width="65.33203125" customWidth="1"/>
+    <col min="6" max="1025" width="11.5546875"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -651,518 +762,528 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="0" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="0" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="0" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="2" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="0" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="B14" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="0" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="B15" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="0" t="s">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="B16" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="0" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="B17" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="0" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="B18" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="0" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="0" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="B20" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="0" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="B21" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="0" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="B22" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="0" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="B23" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="0" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="B24" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="0" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="0" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="B26" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="0" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="B27" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="0" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="B28" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="0" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="B29" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="0" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="B30" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="0" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="B31" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="0" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="B32" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="0" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="B33" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="0" t="s">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="B34" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="0" t="s">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="B35" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="0" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="B36" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="0" t="s">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="B37" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="0" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="B38" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="0" t="s">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="B39" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="0" t="s">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="B40" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="0" t="s">
+    </row>
+    <row r="41" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="0" t="s">
+      <c r="D41" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="3" t="s">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="0" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="0" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="0" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="0" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="0" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" s="0" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="0" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48" s="0" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="0" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="0" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="0" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" s="0" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="B53" s="0" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" s="0" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="0" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B56" s="0" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="B57" s="0" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="B58" s="0" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="B59" s="0" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="B60" s="0" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="B61" s="0" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="0" t="s">
+      <c r="D69" t="s">
         <v>104</v>
       </c>
-      <c r="D68" s="0" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="0" t="s">
-        <v>103</v>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="D9:D12"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
@@ -1171,56 +1292,6 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
@@ -1228,23 +1299,23 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="93d2b372-37bc-474e-a2f6-e237b07f4f3a">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <_dlc_DocId xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">TMFEV-885672295-4168</_dlc_DocId>
+    <_dlc_DocId xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">TMFEV-885672295-4175</_dlc_DocId>
     <_dlc_DocIdUrl xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">
-      <Url>https://tmfev.sharepoint.com/sites/tmf/mi-i/_layouts/15/DocIdRedir.aspx?ID=TMFEV-885672295-4168</Url>
-      <Description>TMFEV-885672295-4168</Description>
+      <Url>https://tmfev.sharepoint.com/sites/tmf/mi-i/_layouts/15/DocIdRedir.aspx?ID=TMFEV-885672295-4175</Url>
+      <Description>TMFEV-885672295-4175</Description>
     </_dlc_DocIdUrl>
   </documentManagement>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100370F783D856BE247B308870A0815A245" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e59e6bd7546e62b090aef4fb5ed9afb6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15b42a90-06dd-4669-ae82-892e5974bb2f" xmlns:ns3="93d2b372-37bc-474e-a2f6-e237b07f4f3a" xmlns:ns4="2d89f73c-94c0-4155-aa8d-969ee56d6579" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4ca942eca7b8d364d6ad20a4d456e115" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="15b42a90-06dd-4669-ae82-892e5974bb2f"/>
@@ -1509,18 +1580,99 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B8B0EA-3BDF-4954-AE09-AB5AAF359A99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1817AC26-B6E2-4C47-BB33-95CC1107F6F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1817AC26-B6E2-4C47-BB33-95CC1107F6F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E64479-D726-4AB8-A716-1F18B611E8E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="15b42a90-06dd-4669-ae82-892e5974bb2f"/>
+    <ds:schemaRef ds:uri="93d2b372-37bc-474e-a2f6-e237b07f4f3a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E64479-D726-4AB8-A716-1F18B611E8E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB6B2F1-2C78-4FE6-AF5B-CDBBCB8A75BF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="15b42a90-06dd-4669-ae82-892e5974bb2f"/>
+    <ds:schemaRef ds:uri="93d2b372-37bc-474e-a2f6-e237b07f4f3a"/>
+    <ds:schemaRef ds:uri="2d89f73c-94c0-4155-aa8d-969ee56d6579"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB6B2F1-2C78-4FE6-AF5B-CDBBCB8A75BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B8B0EA-3BDF-4954-AE09-AB5AAF359A99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/R-dataprocessor/submodules/manual_start/Fallvignette_Process_Evaluation/R-Fallvignette_Process_Evaluation/inst/extdata/WP8MRP_Liste_Daten_Mapping20260722.xlsx
+++ b/R-dataprocessor/submodules/manual_start/Fallvignette_Process_Evaluation/R-Fallvignette_Process_Evaluation/inst/extdata/WP8MRP_Liste_Daten_Mapping20260722.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{EE6A06D7-04C5-4693-89AC-F1482AA91ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7BDE5A9-AD65-4507-AC16-D90695611332}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{EE6A06D7-04C5-4693-89AC-F1482AA91ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E97DF81-D74D-4470-8A66-A9D79154D81D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="111">
   <si>
     <t>Fallvignette</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>Standortübergreifend eindeutig</t>
+  </si>
+  <si>
+    <t>wp8_ret_id</t>
+  </si>
+  <si>
+    <t>ret_id</t>
   </si>
   <si>
     <t>wp8_standort_id</t>
@@ -752,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.15"/>
   <cols>
     <col min="1" max="1" width="54.85546875" customWidth="1"/>
@@ -787,15 +793,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="12.75">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -805,6 +808,9 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
@@ -813,15 +819,15 @@
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -841,31 +847,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="12.75" customHeight="1">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="B9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" ht="12.75" customHeight="1">
       <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="3"/>
@@ -874,9 +879,10 @@
       <c r="A13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>27</v>
       </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
@@ -1094,31 +1100,31 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="24">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="12.75">
+    <row r="42" spans="1:4" ht="24">
       <c r="A42" t="s">
         <v>38</v>
       </c>
       <c r="B42" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="D42" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="12.75">
       <c r="A43" t="s">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1126,7 +1132,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1134,7 +1140,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1142,7 +1148,7 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1150,7 +1156,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1158,7 +1164,7 @@
         <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1166,7 +1172,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1174,7 +1180,7 @@
         <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1182,7 +1188,7 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1190,7 +1196,7 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1198,7 +1204,7 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1206,7 +1212,7 @@
         <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1214,7 +1220,7 @@
         <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1222,7 +1228,7 @@
         <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1230,7 +1236,7 @@
         <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1238,7 +1244,7 @@
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1246,7 +1252,7 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1254,7 +1260,7 @@
         <v>74</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1262,7 +1268,7 @@
         <v>76</v>
       </c>
       <c r="B61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1270,7 +1276,7 @@
         <v>78</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1278,30 +1284,38 @@
         <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" t="s">
         <v>107</v>
       </c>
-      <c r="D70" t="s">
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="97" spans="3:3">
-      <c r="C97" t="s">
-        <v>106</v>
+    <row r="71" spans="1:4">
+      <c r="B71" t="s">
+        <v>109</v>
+      </c>
+      <c r="D71" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3">
+      <c r="C98" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="D10:D13"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1313,6 +1327,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -1362,32 +1385,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="93d2b372-37bc-474e-a2f6-e237b07f4f3a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_dlc_DocId xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">TMFEV-885672295-4175</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">
-      <Url>https://tmfev.sharepoint.com/sites/tmf/mi-i/_layouts/15/DocIdRedir.aspx?ID=TMFEV-885672295-4175</Url>
-      <Description>TMFEV-885672295-4175</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100370F783D856BE247B308870A0815A245" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e59e6bd7546e62b090aef4fb5ed9afb6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15b42a90-06dd-4669-ae82-892e5974bb2f" xmlns:ns3="93d2b372-37bc-474e-a2f6-e237b07f4f3a" xmlns:ns4="2d89f73c-94c0-4155-aa8d-969ee56d6579" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4ca942eca7b8d364d6ad20a4d456e115" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="15b42a90-06dd-4669-ae82-892e5974bb2f"/>
@@ -1652,18 +1650,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="93d2b372-37bc-474e-a2f6-e237b07f4f3a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_dlc_DocId xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">TMFEV-885672295-4175</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">
+      <Url>https://tmfev.sharepoint.com/sites/tmf/mi-i/_layouts/15/DocIdRedir.aspx?ID=TMFEV-885672295-4175</Url>
+      <Description>TMFEV-885672295-4175</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1817AC26-B6E2-4C47-BB33-95CC1107F6F8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B8B0EA-3BDF-4954-AE09-AB5AAF359A99}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1817AC26-B6E2-4C47-BB33-95CC1107F6F8}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E64479-D726-4AB8-A716-1F18B611E8E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB6B2F1-2C78-4FE6-AF5B-CDBBCB8A75BF}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB6B2F1-2C78-4FE6-AF5B-CDBBCB8A75BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E64479-D726-4AB8-A716-1F18B611E8E6}"/>
 </file>
--- a/R-dataprocessor/submodules/manual_start/Fallvignette_Process_Evaluation/R-Fallvignette_Process_Evaluation/inst/extdata/WP8MRP_Liste_Daten_Mapping20260722.xlsx
+++ b/R-dataprocessor/submodules/manual_start/Fallvignette_Process_Evaluation/R-Fallvignette_Process_Evaluation/inst/extdata/WP8MRP_Liste_Daten_Mapping20260722.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{EE6A06D7-04C5-4693-89AC-F1482AA91ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E97DF81-D74D-4470-8A66-A9D79154D81D}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{EE6A06D7-04C5-4693-89AC-F1482AA91ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E313BC3E-37A0-4B6A-8EF9-7F135C944E00}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>Fallvignette</t>
   </si>
@@ -196,114 +196,6 @@
     <t>ret_gewiss_grund_abl_klin1_neg</t>
   </si>
   <si>
-    <t>wp8_ret_massn_am___1</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___1</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_am___2</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___2</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_am___3</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___3</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_am___4</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___4</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_am___5</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___5</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_am___6</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___6</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_am___7</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___7</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_am___8</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___8</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_am___9</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___9</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_am___10</t>
-  </si>
-  <si>
-    <t>ret_massn_am1___10</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_orga___1</t>
-  </si>
-  <si>
-    <t>ret_massn_orga1___1</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_orga___2</t>
-  </si>
-  <si>
-    <t>ret_massn_orga1___2</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_orga___3</t>
-  </si>
-  <si>
-    <t>ret_massn_orga1___3</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_orga___4</t>
-  </si>
-  <si>
-    <t>ret_massn_orga1___4</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_orga___5</t>
-  </si>
-  <si>
-    <t>ret_massn_orga1___5</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_orga___6</t>
-  </si>
-  <si>
-    <t>ret_massn_orga1___6</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_orga___7</t>
-  </si>
-  <si>
-    <t>ret_massn_orga1___7</t>
-  </si>
-  <si>
-    <t>wp8_ret_massn_orga___8</t>
-  </si>
-  <si>
-    <t>ret_massn_orga1___8</t>
-  </si>
-  <si>
     <t>wp8_ret_notiz</t>
   </si>
   <si>
@@ -311,79 +203,25 @@
   </si>
   <si>
     <t>ret_gewissheit2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ret_gewiss_grund2_abl_01 </t>
+  </si>
+  <si>
+    <t>ret_gewiss_grund_abl_klin2</t>
+  </si>
+  <si>
+    <t>ret_gewiss_grund_abl_klin2_neg</t>
+  </si>
+  <si>
+    <t>ret_notiz2</t>
+  </si>
+  <si>
+    <t>mrp_auswahl_complete</t>
   </si>
   <si>
     <t>Ein retMRP kann zwei Bewertungen haben,
 Die je eine eigene Zeile bekommen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ret_gewiss_grund2_abl_01 </t>
-  </si>
-  <si>
-    <t>ret_gewiss_grund_abl_klin2</t>
-  </si>
-  <si>
-    <t>ret_gewiss_grund_abl_klin2_neg</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___1</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___2</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___3</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___4</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___5</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___6</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___7</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___8</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___9</t>
-  </si>
-  <si>
-    <t>ret_massn_am2___10</t>
-  </si>
-  <si>
-    <t>ret_massn_orga2___1</t>
-  </si>
-  <si>
-    <t>ret_massn_orga2___2</t>
-  </si>
-  <si>
-    <t>ret_massn_orga2___3</t>
-  </si>
-  <si>
-    <t>ret_massn_orga2___4</t>
-  </si>
-  <si>
-    <t>ret_massn_orga2___5</t>
-  </si>
-  <si>
-    <t>ret_massn_orga2___6</t>
-  </si>
-  <si>
-    <t>ret_massn_orga2___7</t>
-  </si>
-  <si>
-    <t>ret_massn_orga2___8</t>
-  </si>
-  <si>
-    <t>ret_notiz2</t>
-  </si>
-  <si>
-    <t>mrp_auswahl_complete</t>
   </si>
   <si>
     <t>Select wenn Broad Consent und (ret_gewiss_grund1_abl_01 und/oder ret_gewiss_grund2_abl_01 =3)</t>
@@ -908,7 +746,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -916,7 +754,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -924,7 +762,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -932,7 +770,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -940,7 +778,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -948,7 +786,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -956,7 +794,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>46</v>
       </c>
@@ -964,353 +802,71 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="B24" t="s">
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
         <v>50</v>
       </c>
-      <c r="B25" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
         <v>52</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:4" ht="24">
+      <c r="D42" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="43" spans="4:4" ht="12.75"/>
+    <row r="71" spans="2:4">
+      <c r="B71" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
+      <c r="D71" t="s">
         <v>56</v>
-      </c>
-      <c r="B28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="24">
-      <c r="A42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="12.75">
-      <c r="A43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>50</v>
-      </c>
-      <c r="B48" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>64</v>
-      </c>
-      <c r="B55" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>68</v>
-      </c>
-      <c r="B57" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>70</v>
-      </c>
-      <c r="B58" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>72</v>
-      </c>
-      <c r="B59" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>74</v>
-      </c>
-      <c r="B60" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>76</v>
-      </c>
-      <c r="B61" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>78</v>
-      </c>
-      <c r="B62" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>82</v>
-      </c>
-      <c r="B64" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="B71" t="s">
-        <v>109</v>
-      </c>
-      <c r="D71" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="98" spans="3:3">
       <c r="C98" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1336,53 +892,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="93d2b372-37bc-474e-a2f6-e237b07f4f3a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_dlc_DocId xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">TMFEV-885672295-4175</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">
+      <Url>https://tmfev.sharepoint.com/sites/tmf/mi-i/_layouts/15/DocIdRedir.aspx?ID=TMFEV-885672295-4175</Url>
+      <Description>TMFEV-885672295-4175</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1651,19 +1173,53 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="93d2b372-37bc-474e-a2f6-e237b07f4f3a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_dlc_DocId xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">TMFEV-885672295-4175</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f">
-      <Url>https://tmfev.sharepoint.com/sites/tmf/mi-i/_layouts/15/DocIdRedir.aspx?ID=TMFEV-885672295-4175</Url>
-      <Description>TMFEV-885672295-4175</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1671,7 +1227,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B8B0EA-3BDF-4954-AE09-AB5AAF359A99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E64479-D726-4AB8-A716-1F18B611E8E6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1679,5 +1235,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E64479-D726-4AB8-A716-1F18B611E8E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B8B0EA-3BDF-4954-AE09-AB5AAF359A99}"/>
 </file>
--- a/R-dataprocessor/submodules/manual_start/Fallvignette_Process_Evaluation/R-Fallvignette_Process_Evaluation/inst/extdata/WP8MRP_Liste_Daten_Mapping20260722.xlsx
+++ b/R-dataprocessor/submodules/manual_start/Fallvignette_Process_Evaluation/R-Fallvignette_Process_Evaluation/inst/extdata/WP8MRP_Liste_Daten_Mapping20260722.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{EE6A06D7-04C5-4693-89AC-F1482AA91ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E313BC3E-37A0-4B6A-8EF9-7F135C944E00}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{EE6A06D7-04C5-4693-89AC-F1482AA91ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE2BCB6E-6C63-4317-A6AC-B181C8ECA664}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,13 +187,13 @@
     <t>wp8_ret_gewiss_grund_abl_klin</t>
   </si>
   <si>
-    <t xml:space="preserve">ret_gewiss_grund_abl_klin1 </t>
-  </si>
-  <si>
-    <t>wp8_ret_gewiss_grund_abl_klin_neg</t>
-  </si>
-  <si>
-    <t>ret_gewiss_grund_abl_klin1_neg</t>
+    <t>ret_gewiss_grund_abl_klin1</t>
+  </si>
+  <si>
+    <t>wp8_ret_gewiss_grund_abl_klin_neg___1</t>
+  </si>
+  <si>
+    <t>ret_gewiss_grund_abl_klin1_neg___1</t>
   </si>
   <si>
     <t>wp8_ret_notiz</t>
@@ -211,7 +211,7 @@
     <t>ret_gewiss_grund_abl_klin2</t>
   </si>
   <si>
-    <t>ret_gewiss_grund_abl_klin2_neg</t>
+    <t>ret_gewiss_grund_abl_klin2_neg___1</t>
   </si>
   <si>
     <t>ret_notiz2</t>
@@ -883,15 +883,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="15b42a90-06dd-4669-ae82-892e5974bb2f" xsi:nil="true"/>
@@ -907,7 +898,66 @@
 </p:properties>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100370F783D856BE247B308870A0815A245" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e59e6bd7546e62b090aef4fb5ed9afb6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15b42a90-06dd-4669-ae82-892e5974bb2f" xmlns:ns3="93d2b372-37bc-474e-a2f6-e237b07f4f3a" xmlns:ns4="2d89f73c-94c0-4155-aa8d-969ee56d6579" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4ca942eca7b8d364d6ad20a4d456e115" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="15b42a90-06dd-4669-ae82-892e5974bb2f"/>
@@ -1172,68 +1222,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E64479-D726-4AB8-A716-1F18B611E8E6}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1817AC26-B6E2-4C47-BB33-95CC1107F6F8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E64479-D726-4AB8-A716-1F18B611E8E6}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB6B2F1-2C78-4FE6-AF5B-CDBBCB8A75BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B8B0EA-3BDF-4954-AE09-AB5AAF359A99}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08B8B0EA-3BDF-4954-AE09-AB5AAF359A99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB6B2F1-2C78-4FE6-AF5B-CDBBCB8A75BF}"/>
 </file>